--- a/dados/fonte/Expansao_America_do_Sul.xlsx
+++ b/dados/fonte/Expansao_America_do_Sul.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Ligas" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Decisões" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Legenda" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Pesquisa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -639,7 +640,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Buenos Aires Sul</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -735,7 +736,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Buenos Aires Norte</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -1023,7 +1024,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Buenos Aires Sul</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1119,7 +1120,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Buenos Aires Oeste</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -2175,7 +2176,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Buenos Aires Sul</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -3766,7 +3767,7 @@
           <t>Islas Malvinas</t>
         </is>
       </c>
-      <c r="H35" s="2" t="n">
+      <c r="H35" t="n">
         <v>21500</v>
       </c>
       <c r="I35" t="inlineStr">
@@ -4054,8 +4055,8 @@
           <t>Don León Kolbowski</t>
         </is>
       </c>
-      <c r="H38" s="2" t="n">
-        <v>14000</v>
+      <c r="H38" t="n">
+        <v>18000</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -4342,8 +4343,8 @@
           <t>Chacarita Juniors</t>
         </is>
       </c>
-      <c r="H41" s="2" t="n">
-        <v>25000</v>
+      <c r="H41" t="n">
+        <v>24300</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -4535,7 +4536,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>40000</v>
+        <v>33716</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -5302,8 +5303,8 @@
           <t>Ricardo Etcheverri</t>
         </is>
       </c>
-      <c r="H51" s="2" t="n">
-        <v>24442</v>
+      <c r="H51" t="n">
+        <v>24268</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -5782,8 +5783,8 @@
           <t>Eduardo Gallardón</t>
         </is>
       </c>
-      <c r="H56" s="2" t="n">
-        <v>34000</v>
+      <c r="H56" t="n">
+        <v>38000</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -5974,8 +5975,8 @@
           <t>República de Mataderos</t>
         </is>
       </c>
-      <c r="H58" s="2" t="n">
-        <v>28500</v>
+      <c r="H58" t="n">
+        <v>28000</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -6454,8 +6455,8 @@
           <t>La Ciudadela</t>
         </is>
       </c>
-      <c r="H63" s="2" t="n">
-        <v>30000</v>
+      <c r="H63" t="n">
+        <v>30250</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -6838,8 +6839,8 @@
           <t>Alfredo Beranger</t>
         </is>
       </c>
-      <c r="H67" s="2" t="n">
-        <v>15000</v>
+      <c r="H67" t="n">
+        <v>19500</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -7798,7 +7799,7 @@
           <t>Nueva España</t>
         </is>
       </c>
-      <c r="H77" s="2" t="n">
+      <c r="H77" t="n">
         <v>32500</v>
       </c>
       <c r="I77" t="inlineStr">
@@ -12119,7 +12120,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>21414</v>
+        <v>21113</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -12215,7 +12216,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>12346</v>
+        <v>12102</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -15574,8 +15575,8 @@
           <t>Guillermo Plazas Alcid</t>
         </is>
       </c>
-      <c r="H158" s="2" t="n">
-        <v>26000</v>
+      <c r="H158" t="n">
+        <v>27000</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -15766,8 +15767,8 @@
           <t>General Santander</t>
         </is>
       </c>
-      <c r="H160" s="2" t="n">
-        <v>42000</v>
+      <c r="H160" t="n">
+        <v>42901</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -21567,7 +21568,7 @@
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>Montevidéu Oeste</t>
+          <t>Montevidéu</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
@@ -21663,7 +21664,7 @@
       </c>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>Montevidéu Centro</t>
+          <t>Montevidéu</t>
         </is>
       </c>
       <c r="R221" t="inlineStr">
@@ -21759,7 +21760,7 @@
       </c>
       <c r="Q222" t="inlineStr">
         <is>
-          <t>Montevidéu Centro</t>
+          <t>Montevidéu</t>
         </is>
       </c>
       <c r="R222" t="inlineStr">
@@ -21855,7 +21856,7 @@
       </c>
       <c r="Q223" t="inlineStr">
         <is>
-          <t>Montevidéu Oeste</t>
+          <t>Montevidéu</t>
         </is>
       </c>
       <c r="R223" t="inlineStr">
@@ -21951,7 +21952,7 @@
       </c>
       <c r="Q224" t="inlineStr">
         <is>
-          <t>Montevidéu Norte</t>
+          <t>Montevidéu</t>
         </is>
       </c>
       <c r="R224" t="inlineStr">
@@ -22047,7 +22048,7 @@
       </c>
       <c r="Q225" t="inlineStr">
         <is>
-          <t>Montevidéu Norte</t>
+          <t>Montevidéu</t>
         </is>
       </c>
       <c r="R225" t="inlineStr">
@@ -22143,7 +22144,7 @@
       </c>
       <c r="Q226" t="inlineStr">
         <is>
-          <t>Montevidéu Norte</t>
+          <t>Montevidéu Leste</t>
         </is>
       </c>
       <c r="R226" t="inlineStr">
@@ -22335,7 +22336,7 @@
       </c>
       <c r="Q228" t="inlineStr">
         <is>
-          <t>Montevidéu Norte</t>
+          <t>Montevidéu Oeste</t>
         </is>
       </c>
       <c r="R228" t="inlineStr">
@@ -22431,7 +22432,7 @@
       </c>
       <c r="Q229" t="inlineStr">
         <is>
-          <t>Montevidéu Centro</t>
+          <t>Montevidéu Leste</t>
         </is>
       </c>
       <c r="R229" t="inlineStr">
@@ -22623,7 +22624,7 @@
       </c>
       <c r="Q231" t="inlineStr">
         <is>
-          <t>Montevidéu Centro</t>
+          <t>Montevidéu Leste</t>
         </is>
       </c>
       <c r="R231" t="inlineStr">
@@ -22911,7 +22912,7 @@
       </c>
       <c r="Q234" t="inlineStr">
         <is>
-          <t>Montevidéu Norte</t>
+          <t>Montevidéu Leste</t>
         </is>
       </c>
       <c r="R234" t="inlineStr">
@@ -23199,7 +23200,7 @@
       </c>
       <c r="Q237" t="inlineStr">
         <is>
-          <t>Andes Venezuelanos</t>
+          <t>Oeste da Venezuela</t>
         </is>
       </c>
       <c r="R237" t="inlineStr">
@@ -23583,7 +23584,7 @@
       </c>
       <c r="Q241" t="inlineStr">
         <is>
-          <t>Andes Venezuelanos</t>
+          <t>Oeste da Venezuela</t>
         </is>
       </c>
       <c r="R241" t="inlineStr">
@@ -23967,7 +23968,7 @@
       </c>
       <c r="Q245" t="inlineStr">
         <is>
-          <t>Maracaibo</t>
+          <t>Oeste da Venezuela</t>
         </is>
       </c>
       <c r="R245" t="inlineStr">
@@ -24446,7 +24447,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Buenos Aires Norte</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -24455,7 +24456,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -24471,7 +24472,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Buenos Aires Oeste</t>
+          <t>Buenos Aires Norte</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -24480,7 +24481,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -24496,7 +24497,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Buenos Aires Sul</t>
+          <t>Buenos Aires Oeste</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -24505,7 +24506,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -24521,7 +24522,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cuyo e Patagônia</t>
+          <t>Buenos Aires Sul</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -24530,11 +24531,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Puerto Madryn, San Juan</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -24546,7 +24547,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Cuyo e Patagônia</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -24555,11 +24556,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Córdoba, Río Cuarto</t>
+          <t>Puerto Madryn, San Juan</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -24571,7 +24572,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Interior de Buenos Aires</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -24580,11 +24581,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Campana, Carlos Casares, Junín, Mar del Plata, Zárate</t>
+          <t>Córdoba, Río Cuarto</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -24596,7 +24597,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>La Matanza</t>
+          <t>Interior de Buenos Aires</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -24605,11 +24606,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Gregorio de Laferrere, Isidro Casanova</t>
+          <t>Campana, Carlos Casares, Junín, Mar del Plata, Zárate</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -24621,7 +24622,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>La Plata</t>
+          <t>La Matanza</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -24630,11 +24631,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Berisso, La Plata</t>
+          <t>Gregorio de Laferrere, Isidro Casanova</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -24646,7 +24647,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lanús e Lomas</t>
+          <t>La Plata</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -24655,11 +24656,11 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Adrogué, Banfield, Lanús, Lomas de Zamora, Remedios de Escalada, Temperley</t>
+          <t>Berisso, La Plata</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -24671,7 +24672,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Litoral Argentino</t>
+          <t>Lanús e Lomas</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -24680,11 +24681,11 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Paraná, Rafaela, Santa Fe</t>
+          <t>Adrogué, Banfield, Lanús, Lomas de Zamora, Remedios de Escalada, Temperley</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -24696,7 +24697,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Litoral Argentino</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -24709,7 +24710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Maipú, Mendoza</t>
+          <t>Paraná, Rafaela, Santa Fe</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -24721,7 +24722,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Morón e Merlo</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -24730,11 +24731,11 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ituzaingó, Libertad, Merlo, Morón, San Miguel</t>
+          <t>Maipú, Mendoza</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -24746,7 +24747,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Norte da Argentina</t>
+          <t>Morón e Merlo</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -24755,11 +24756,11 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Resistencia, Salta, San Salvador de Jujuy</t>
+          <t>Ituzaingó, Libertad, Merlo, Morón, San Miguel</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -24771,7 +24772,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Norte de Buenos Aires</t>
+          <t>Norte da Argentina</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -24780,11 +24781,11 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Boulogne, Ingeniero Maschwitz, Munro, Pilar, Vicente López, Victoria</t>
+          <t>Resistencia, Salta, San Salvador de Jujuy</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -24796,7 +24797,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Quilmes e Berazategui</t>
+          <t>Norte de Buenos Aires</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -24805,11 +24806,11 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Boulogne, Ingeniero Maschwitz, Munro, Pilar, Vicente López, Victoria</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -24821,7 +24822,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rosario</t>
+          <t>Quilmes e Berazategui</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -24834,7 +24835,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Rosario</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -24846,7 +24847,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>San Martín e Tres de Febrero</t>
+          <t>Rosario</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -24855,11 +24856,11 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Caseros, José Ingenieros, Loma Hermosa, San Martín, Villa Lynch</t>
+          <t>Rosario</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -24871,7 +24872,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Santiago del Estero</t>
+          <t>San Martín e Tres de Febrero</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -24880,11 +24881,11 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Santiago del Estero</t>
+          <t>Caseros, José Ingenieros, Loma Hermosa, San Martín, Villa Lynch</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -24896,7 +24897,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tucumán</t>
+          <t>Santiago del Estero</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -24905,11 +24906,11 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>San Miguel de Tucumán</t>
+          <t>Santiago del Estero</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -24921,7 +24922,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Varela e Ezeiza</t>
+          <t>Tucumán</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -24930,11 +24931,11 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cañuelas, Ezeiza, Florencio Varela</t>
+          <t>San Miguel de Tucumán</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -24946,12 +24947,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Varela e Ezeiza</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -24959,7 +24960,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cochabamba, Vinto</t>
+          <t>Cañuelas, Ezeiza, Florencio Varela</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -24971,7 +24972,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Interior da Bolívia</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -24984,7 +24985,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Entre Ríos, Montero, Tarija</t>
+          <t>Cochabamba, Vinto</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -24996,7 +24997,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Interior da Bolívia</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -25009,7 +25010,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>El Alto, La Paz</t>
+          <t>Entre Ríos, Montero, Tarija</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -25021,7 +25022,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Oruro e Potosí</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -25030,11 +25031,11 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Oruro, Potosí, Sucre</t>
+          <t>El Alto, La Paz</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -25046,7 +25047,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Oruro e Potosí</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -25055,11 +25056,11 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Oruro, Potosí, Sucre</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -25071,20 +25072,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Centro do Chile</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Curicó, Rancagua, Santa Cruz, Talca</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -25096,7 +25097,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Centro do Chile</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -25105,11 +25106,11 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Concepción, Talcahuano</t>
+          <t>Curicó, Rancagua, Santa Cruz, Talca</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -25121,7 +25122,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Norte Chico</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -25134,7 +25135,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Coquimbo, El Salvador, La Serena</t>
+          <t>Concepción, Talcahuano</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -25146,7 +25147,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Norte do Chile</t>
+          <t>Norte Chico</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -25155,11 +25156,11 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Antofagasta, Arica, Calama, Copiapó, Iquique</t>
+          <t>Coquimbo, El Salvador, La Serena</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -25171,7 +25172,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Norte do Chile</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -25184,7 +25185,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Antofagasta, Arica, Calama, Copiapó, Iquique</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -25196,7 +25197,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Santiago Sul</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -25209,7 +25210,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>San Bernardo, Santiago</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -25221,7 +25222,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sul do Chile</t>
+          <t>Santiago Sul</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -25230,11 +25231,11 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Chillán, Temuco</t>
+          <t>San Bernardo, Santiago</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -25246,7 +25247,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Sul do Chile</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -25255,11 +25256,11 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>La Calera, Limache, Quillota, Valparaíso, Viña del Mar</t>
+          <t>Chillán, Temuco</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -25271,20 +25272,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Colômbia</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>La Calera, Limache, Quillota, Valparaíso, Viña del Mar</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -25296,7 +25297,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Bogotá Sul</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -25309,7 +25310,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Bogotá, Zipaquirá</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -25321,7 +25322,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá Sul</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -25330,11 +25331,11 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cali, Palmira</t>
+          <t>Bogotá, Zipaquirá</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -25346,7 +25347,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Costa Colombiana</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -25355,11 +25356,11 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Barranquilla, Cartagena, Montería, Santa Marta</t>
+          <t>Cali, Palmira</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -25371,7 +25372,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Eixo Cafeteiro</t>
+          <t>Costa Colombiana</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -25380,11 +25381,11 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Manizales, Pereira</t>
+          <t>Barranquilla, Cartagena, Montería, Santa Marta</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -25396,7 +25397,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Interior da Colômbia</t>
+          <t>Eixo Cafeteiro</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -25405,11 +25406,11 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tunja, Valledupar, Villavicencio</t>
+          <t>Manizales, Pereira</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -25421,7 +25422,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Interior da Colômbia</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -25430,11 +25431,11 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Envigado, Itagüí, Medellín, Rionegro</t>
+          <t>Tunja, Valledupar, Villavicencio</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -25446,7 +25447,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Norte da Colômbia</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -25455,11 +25456,11 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Bucaramanga, Cúcuta, Floridablanca</t>
+          <t>Envigado, Itagüí, Medellín, Rionegro</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -25471,7 +25472,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sul da Colômbia</t>
+          <t>Norte da Colômbia</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -25484,7 +25485,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ibagué, Neiva, Pasto</t>
+          <t>Bucaramanga, Cúcuta, Floridablanca</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -25496,12 +25497,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ambato</t>
+          <t>Sul da Colômbia</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Equador</t>
+          <t>Colômbia</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -25509,7 +25510,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ambato</t>
+          <t>Ibagué, Neiva, Pasto</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -25521,7 +25522,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Costa Equatoriana</t>
+          <t>Ambato</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -25534,7 +25535,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Machala, Manta</t>
+          <t>Ambato</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -25546,7 +25547,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Guayaquil</t>
+          <t>Costa Equatoriana</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -25555,11 +25556,11 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Guayaquil</t>
+          <t>Machala, Manta</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -25571,7 +25572,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Quito</t>
+          <t>Guayaquil</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -25580,11 +25581,11 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Quito, Sangolquí</t>
+          <t>Guayaquil</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -25596,7 +25597,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sul do Equador</t>
+          <t>Quito</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -25605,11 +25606,11 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Cuenca, Loja</t>
+          <t>Quito, Sangolquí</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -25621,20 +25622,20 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Assunção</t>
+          <t>Sul do Equador</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Paraguai</t>
+          <t>Equador</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Assunção</t>
+          <t>Cuenca, Loja</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -25646,7 +25647,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Grande Assunção</t>
+          <t>Assunção</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -25659,7 +25660,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Assunção, Luque</t>
+          <t>Assunção</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -25671,7 +25672,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Interior do Paraguai</t>
+          <t>Grande Assunção</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -25680,11 +25681,11 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Juan León Mallorquín, Pedro Juan Caballero</t>
+          <t>Assunção, Luque</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -25696,20 +25697,20 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cusco</t>
+          <t>Interior do Paraguai</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Paraguai</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Cusco</t>
+          <t>Juan León Mallorquín, Pedro Juan Caballero</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -25721,7 +25722,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Cusco</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -25730,11 +25731,11 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Callao, Lima</t>
+          <t>Cusco</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -25746,7 +25747,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Norte do Peru</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -25755,11 +25756,11 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cajamarca, Chongoyape, Cutervo, Huánuco, Piura, Sullana</t>
+          <t>Callao, Lima</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -25771,7 +25772,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sul do Peru</t>
+          <t>Norte do Peru</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -25780,11 +25781,11 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Andahuaylas, Arequipa, Ayacucho, Huancayo, Tarma</t>
+          <t>Cajamarca, Chongoyape, Cutervo, Huánuco, Piura, Sullana</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -25796,20 +25797,20 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Interior do Uruguai</t>
+          <t>Sul do Peru</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Uruguai</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Colonia del Sacramento, Las Piedras, Melo</t>
+          <t>Andahuaylas, Arequipa, Ayacucho, Huancayo, Tarma</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -25821,7 +25822,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Montevidéu Centro</t>
+          <t>Interior do Uruguai</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25830,11 +25831,11 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Montevidéu</t>
+          <t>Colonia del Sacramento, Las Piedras, Melo</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -25846,7 +25847,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Montevidéu Norte</t>
+          <t>Montevidéu</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25855,7 +25856,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -25871,7 +25872,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Montevidéu Oeste</t>
+          <t>Montevidéu Leste</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -25896,20 +25897,20 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Andes Venezuelanos</t>
+          <t>Montevidéu Oeste</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Uruguai</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Mérida, San Cristóbal</t>
+          <t>Montevidéu</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -25971,7 +25972,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Maracaibo</t>
+          <t>Oeste da Venezuela</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -25980,11 +25981,11 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Maracaibo</t>
+          <t>Maracaibo, Mérida, San Cristóbal</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -26743,4 +26744,279 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clube</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Capacidade conferida</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Fonte / observação</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ferro</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>24268</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>clube e imprensa: 24.268 (projeto de ampliação vai a 27.000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Chacarita</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>24300</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>obra em curso soma 5.240 e leva a 29.540</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Nueva Chicago</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>28000</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ceroacero e fichajes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>site oficial do clube</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Temperley</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>19500</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>oficial do clube diz 26.000; a medida em uso é 19.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>All Boys</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>21500</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>valor de referência do clube</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Los Andes</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>38000</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>maior estádio da Primera Nacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Quilmes</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>30200</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>26.000 em pé e 4.200 sentados</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Colón</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>33716</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>aforo oficial; havia fonte com 40.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Deportivo Español</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>32500</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ampliado em 1996</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>San Martín Tucumán</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>30250</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>clube</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Santiago Wanderers</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>21113</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>stadiumdb; havia fonte com 25.568</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cobreloa</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>12102</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>estádio municipal de Calama, reinaugurado em 2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Cúcuta Deportivo</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>42901</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>General Santander</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Atlético Huila</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>27000</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Guillermo Plazas Alcid</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>O que sobrou</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Wikipedia e Transfermarkt estão bloqueados no proxy de saída deste ambiente, então a conferência saiu por busca, um estádio de cada vez. O que não passou por aqui continua amarelo.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>